--- a/src/displayer/ressources/Models parameters.xlsx
+++ b/src/displayer/ressources/Models parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29705"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexis\Documents\Spyder\qtqt_displayer_prjt\qtqt_displayer\src\displayer\ressources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE71FD5-3F0D-4C42-916B-89029D38E890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A84DA4-D88F-4FD0-A38E-694E82A150A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C65AB145-78BA-4340-BED1-F1418AA3D3EB}"/>
   </bookViews>
@@ -287,9 +287,6 @@
     <t>Ginster et al. (2017)</t>
   </si>
   <si>
-    <t xml:space="preserve"> base on Ketcham et using Derycke calibration</t>
-  </si>
-  <si>
     <t>base on Ketcham FT annealing kinetic (negative for DEa resampling)</t>
   </si>
   <si>
@@ -315,6 +312,9 @@
   </si>
   <si>
     <t>helps: all parameters related to cristal modeling methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> base on Ketcham and using Derycke calibration</t>
   </si>
 </sst>
 </file>
@@ -521,7 +521,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -538,7 +538,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -549,7 +548,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -564,27 +563,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -593,18 +583,9 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -614,41 +595,41 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -666,7 +647,7 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -678,11 +659,11 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1024,432 +1005,431 @@
   <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38.28515625" style="13" customWidth="1"/>
-    <col min="3" max="4" width="25.28515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="14" style="6" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="6" customWidth="1"/>
-    <col min="8" max="10" width="11.42578125" style="6"/>
-    <col min="11" max="11" width="36.5703125" style="6" customWidth="1"/>
-    <col min="12" max="12" width="58" style="20" customWidth="1"/>
+    <col min="2" max="2" width="38.28515625" style="12" customWidth="1"/>
+    <col min="3" max="4" width="25.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="11" max="11" width="36.5703125" customWidth="1"/>
+    <col min="12" max="12" width="58" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="55" t="s">
+      <c r="L1" s="46" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
     </row>
     <row r="3" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="10">
         <v>0</v>
       </c>
-      <c r="E3" s="47">
+      <c r="E3" s="38">
         <v>18.93</v>
       </c>
-      <c r="F3" s="45">
+      <c r="F3" s="36">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G3" s="46">
+      <c r="G3" s="37">
         <v>138000</v>
       </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="57"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="48"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="10">
         <v>1</v>
       </c>
-      <c r="E4" s="47">
+      <c r="E4" s="38">
         <v>18.93</v>
       </c>
-      <c r="F4" s="45">
+      <c r="F4" s="36">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="G4" s="46">
+      <c r="G4" s="37">
         <v>109200</v>
       </c>
-      <c r="H4" s="56">
+      <c r="H4" s="47">
         <v>2.3999999999999998E-7</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="12">
         <v>13</v>
       </c>
-      <c r="J4" s="18">
+      <c r="J4" s="12">
         <v>0.22500000000000001</v>
       </c>
-      <c r="K4" s="18">
+      <c r="K4" s="12">
         <v>-5451</v>
       </c>
-      <c r="L4" s="57"/>
+      <c r="L4" s="48"/>
     </row>
     <row r="5" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="10">
         <v>2</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="38">
         <v>19.8</v>
       </c>
-      <c r="F5" s="45">
+      <c r="F5" s="36">
         <v>6.0714000000000002E-5</v>
       </c>
-      <c r="G5" s="46">
+      <c r="G5" s="37">
         <v>122300</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="57"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="48"/>
     </row>
     <row r="6" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="10">
         <v>3</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="38">
         <v>15.65</v>
       </c>
-      <c r="F6" s="45">
+      <c r="F6" s="36">
         <v>19.3188</v>
       </c>
-      <c r="G6" s="46">
+      <c r="G6" s="37">
         <v>165000</v>
       </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="57"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="48"/>
     </row>
     <row r="7" spans="1:12" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="10">
         <v>4</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="38">
         <v>18.93</v>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="36">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="37">
         <v>100100</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="12">
         <v>2.0506984818469548E-7</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="12">
         <f t="shared" ref="I7:K7" si="0">I4</f>
         <v>13</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="12">
         <f t="shared" si="0"/>
         <v>0.22500000000000001</v>
       </c>
-      <c r="K7" s="18">
+      <c r="K7" s="12">
         <f t="shared" si="0"/>
         <v>-5451</v>
       </c>
-      <c r="L7" s="57" t="s">
-        <v>84</v>
+      <c r="L7" s="48" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="10">
         <v>5</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="38">
         <v>18.93</v>
       </c>
-      <c r="F8" s="45">
+      <c r="F8" s="36">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="G8" s="46">
+      <c r="G8" s="37">
         <v>100100</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="12">
         <v>2.0506984818469548E-7</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="12">
         <v>0.83</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="12">
         <v>0</v>
       </c>
-      <c r="K8" s="18">
+      <c r="K8" s="12">
         <v>0</v>
       </c>
-      <c r="L8" s="57" t="s">
-        <v>83</v>
+      <c r="L8" s="48" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="10">
         <v>6</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="38">
         <v>18.93</v>
       </c>
-      <c r="F9" s="45">
+      <c r="F9" s="36">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="37">
         <v>100100</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="12">
         <v>2.0506984818469548E-7</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="12">
         <v>-4.87</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="12">
         <v>1.6799999999999999E-4</v>
       </c>
-      <c r="K9" s="18">
+      <c r="K9" s="12">
         <v>-28.12</v>
       </c>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="48" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="51">
+        <v>-2</v>
+      </c>
+      <c r="E10" s="38">
+        <v>18.93</v>
+      </c>
+      <c r="F10" s="36">
+        <v>6.0714000000000002E-5</v>
+      </c>
+      <c r="G10" s="37">
+        <v>122300</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="58" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="51">
+        <v>-3</v>
+      </c>
+      <c r="E11" s="38">
+        <v>15.65</v>
+      </c>
+      <c r="F11" s="36">
+        <v>6.8999999999999997E-5</v>
+      </c>
+      <c r="G11" s="37">
+        <v>169000</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="10">
+        <v>3</v>
+      </c>
+      <c r="E12" s="38">
+        <v>15.65</v>
+      </c>
+      <c r="F12" s="36">
+        <v>19.3188</v>
+      </c>
+      <c r="G12" s="50">
+        <v>-165000</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="60">
-        <v>-2</v>
-      </c>
-      <c r="E10" s="47">
+      <c r="B13" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="51">
+        <v>-5</v>
+      </c>
+      <c r="E13" s="38">
         <v>18.93</v>
       </c>
-      <c r="F10" s="45">
-        <v>6.0714000000000002E-5</v>
-      </c>
-      <c r="G10" s="46">
-        <v>122300</v>
-      </c>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="60">
-        <v>-3</v>
-      </c>
-      <c r="E11" s="47">
-        <v>15.65</v>
-      </c>
-      <c r="F11" s="45">
-        <v>6.8999999999999997E-5</v>
-      </c>
-      <c r="G11" s="46">
-        <v>169000</v>
-      </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="20" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="23">
-        <v>3</v>
-      </c>
-      <c r="E12" s="47">
-        <v>15.65</v>
-      </c>
-      <c r="F12" s="45">
-        <v>19.3188</v>
-      </c>
-      <c r="G12" s="59">
-        <v>-165000</v>
-      </c>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="58" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="60">
-        <v>-5</v>
-      </c>
-      <c r="E13" s="47">
-        <v>18.93</v>
-      </c>
-      <c r="F13" s="45">
+      <c r="F13" s="36">
         <v>1.9999999999999999E-7</v>
       </c>
-      <c r="G13" s="46">
+      <c r="G13" s="37">
         <v>100100</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="12">
         <v>2.0506984818469548E-7</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="12">
         <v>0.73</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="12">
         <v>0</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="L13" s="20" t="s">
-        <v>82</v>
+      <c r="L13" s="15" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1463,148 +1443,148 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="50.5703125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="50.5703125" style="6" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="26"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="22"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <v>100</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="14" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>102</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <v>105</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="14" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <v>107</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="14" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="16">
         <v>108</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="14" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1619,96 +1599,92 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="23.7109375" style="6" customWidth="1"/>
-    <col min="4" max="4" width="49.42578125" style="20" customWidth="1"/>
+    <col min="1" max="3" width="23.7109375" customWidth="1"/>
+    <col min="4" max="4" width="49.42578125" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>0</v>
       </c>
-      <c r="D3" s="16"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="10">
+        <v>4</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>89</v>
-      </c>
-      <c r="C4" s="11">
-        <v>1</v>
-      </c>
-      <c r="D4" s="16"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="11">
-        <v>2</v>
-      </c>
-      <c r="D5" s="16"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="11">
-        <v>3</v>
-      </c>
-      <c r="D6" s="16"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="11">
-        <v>4</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1718,180 +1694,168 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E281BAD4-77B9-44DC-8065-81AD27F10A33}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" style="29" customWidth="1"/>
-    <col min="2" max="2" width="29" style="31" customWidth="1"/>
-    <col min="3" max="3" width="15" style="31" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" style="33" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="32"/>
+    <col min="1" max="1" width="27.7109375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" style="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="28" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="62"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+    <row r="2" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="23">
+      <c r="C3" s="10">
         <v>-1</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="41">
+      <c r="C4" s="32">
         <v>-2</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="39"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+      <c r="D5" s="30"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="39"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+      <c r="D6" s="30"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="40"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="D7" s="31"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="43"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="D8" s="34"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="41" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="35">
         <v>4</v>
       </c>
-      <c r="D13" s="43"/>
+      <c r="D13" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
